--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1478,74 +1478,6 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>137</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>T24_000000_t35Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>7</v>
-      </c>
-      <c r="D32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>себе стоимость продаж</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>прибыль убыток от продаж</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Pri(ubOtPro</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>140</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>T24_000000_t35Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>7</v>
-      </c>
-      <c r="D33" t="n">
-        <v>4</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>себе стоимость продаж 5 861</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>прибыль убыток от продаж</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Pri(ubOtPro</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,985 +494,713 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14.xlsx</t>
+          <t>T24_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
         <v>3</v>
       </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>текущий налог на прибыль 4 371 599</t>
+          <t>на конец года тысяч рублей себестоимость продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>отложенный налог на прибыль</t>
+          <t>доходы и расходы по обычным видам деятельности за отчетный период себестоимость продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>OtcGoOtlNalNaPri</t>
+          <t>DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas_1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14.xlsx</t>
+          <t>T24_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>текущий налог на прибыль 94 409</t>
+          <t>на конец года тысяч рублей прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>отложенный налог на прибыль</t>
+          <t>отчетный год чистая прибыль убыток отчетного периода</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>OtcGoOtlNalNaPri</t>
+          <t>OtcGoChiPri(ubOtcPer_1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14.xlsx</t>
+          <t>T24_000000_t25OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>текущий налог на прибыль 94 409</t>
+          <t>количество организаций получивших убыток за предыдущий год единиц 52</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>отложенный налог на прибыль</t>
+          <t>количество организаций единиц</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>OtcGoOtlNalNaPri</t>
+          <t>KolOrgEdi_2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14.xlsx</t>
+          <t>T24_000000_t25OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>текущий налог на прибыль 101 698</t>
+          <t>количество организаций получивших убыток за предыдущий год единиц 52</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>отложенный налог на прибыль</t>
+          <t>количество организаций единиц</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>OtcGoOtlNalNaPri</t>
+          <t>KolOrgEdi_2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14.xlsx</t>
+          <t>T24_000000_t25OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>текущий налог на прибыль 101 698</t>
+          <t>количество организаций получивших убыток за предыдущий год единиц</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>отложенный налог на прибыль</t>
+          <t>количество организаций единиц</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>OtcGoOtlNalNaPri</t>
+          <t>KolOrgEdi_2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14.xlsx</t>
+          <t>T24_000000_t25OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>текущий налог на прибыль 126</t>
+          <t>количество организаций получивших убыток за предыдущий год единиц</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.73</v>
+        <v>0.62</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>отложенный налог на прибыль</t>
+          <t>количество организаций единиц</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>OtcGoOtlNalNaPri</t>
+          <t>KolOrgEdi_2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14.xlsx</t>
+          <t>T24_000000_t27Ved14.xlsx</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>текущий налог на прибыль 126</t>
+          <t>в процентах чистая прибыль убыток в ко всем активам 4 6</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.73</v>
+        <v>0.59</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>отложенный налог на прибыль</t>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>OtcGoOtlNalNaPri</t>
+          <t>PriUby(-DoNalV%K:VsAkt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>T24_000000_t27Ved14.xlsx</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей себестоимость продаж с учетом коммерческих и управленческих расходов</t>
+          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 4 7</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.67</v>
+        <v>0.53</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности за отчетный период себестоимость продаж с учетом коммерческих и управленческих расходов</t>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas_1</t>
+          <t>PriUby(-DoNalV%K:VsAkt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>T24_000000_t27Ved14.xlsx</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей прибыль убыток от продаж</t>
+          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 0 3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>отчетный год прибыль убыток до налогообложения</t>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>OtcGoPri(ubDoNal_1</t>
+          <t>PriUby(-DoNalV%K:VsAkt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>T24_000000_t27Ved14.xlsx</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>текущий налог на прибыль</t>
+          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 3 1</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>отчетный год отложенный налог на прибыль</t>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>OtcGoOtlNalNaPri_1</t>
+          <t>PriUby(-DoNalV%K:VsAkt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T24_000000_t25OpfVed14.xlsx</t>
+          <t>T24_000000_t27Ved14.xlsx</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>количество организаций получивших убыток за предыдущий год единиц 52</t>
+          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 2 2</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>количество организаций единиц</t>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>KolOrgEdi_2</t>
+          <t>PriUby(-DoNalV%K:VsAkt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>T24_000000_t25OpfVed14.xlsx</t>
+          <t>T24_000000_t27Ved14.xlsx</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>количество организаций получивших убыток за предыдущий год единиц 52</t>
+          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 15 8</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>количество организаций единиц</t>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>KolOrgEdi_2</t>
+          <t>PriUby(-DoNalV%K:VsAkt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>T24_000000_t25OpfVed14.xlsx</t>
+          <t>T24_000000_t27Ved14.xlsx</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>количество организаций получивших убыток за предыдущий год единиц</t>
+          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 4 6</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>количество организаций единиц</t>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>KolOrgEdi_2</t>
+          <t>PriUby(-DoNalV%K:VsAkt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>T24_000000_t25OpfVed14.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>количество организаций получивших убыток за предыдущий год единиц</t>
+          <t>поступления по финансовой деятельности всего 377 962 851</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>количество организаций единиц</t>
+          <t>платежи по инвестиционной деятельности всего</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>KolOrgEdi_2</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>T24_000000_t27Ved14.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>в процентах чистая прибыль убыток в ко всем активам 4 6</t>
+          <t>поступления по финансовой деятельности всего 377 962 851</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>платежи по инвестиционной деятельности всего</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalV%K:VsAkt</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>T24_000000_t27Ved14.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 4 7</t>
+          <t>поступления по финансовой деятельности всего 34 924 952</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.53</v>
+        <v>0.78</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>платежи по финансовой деятельности всего</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalV%K:VsAkt</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>T24_000000_t27Ved14.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
         <v>4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 0 3</t>
+          <t>поступления по финансовой деятельности всего 34 924 952</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.53</v>
+        <v>0.78</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>платежи по финансовой деятельности всего</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalV%K:VsAkt</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>T24_000000_t27Ved14.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 3 1</t>
+          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalV%K:VsAkt</t>
+          <t>PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>T24_000000_t27Ved14.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
         <v>4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 2 2</t>
+          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalV%K:VsAkt</t>
+          <t>PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>T24_000000_t27Ved14.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D22" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 15 8</t>
+          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalV%K:VsAkt</t>
+          <t>PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>T24_000000_t27Ved14.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D23" t="n">
         <v>4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 4 6</t>
+          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
-        <is>
-          <t>PriUby(-DoNalV%K:VsAkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>124</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" t="n">
-        <v>38</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>поступления по финансовой деятельности всего 377 962 851</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>платежи по инвестиционной деятельности всего</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>PlPoInvDeyt</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>124</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>4</v>
-      </c>
-      <c r="D25" t="n">
-        <v>38</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>поступления по финансовой деятельности всего 377 962 851</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>платежи по инвестиционной деятельности всего</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>PlPoInvDeyt</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>127</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" t="n">
-        <v>4</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>поступления по финансовой деятельности всего 34 924 952</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>платежи по финансовой деятельности всего</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>PlPoFin</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>127</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>поступления по финансовой деятельности всего 34 924 952</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>платежи по финансовой деятельности всего</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>PlPoFin</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>127</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>11</v>
-      </c>
-      <c r="D28" t="n">
-        <v>4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>PlPoFin3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>127</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>12</v>
-      </c>
-      <c r="D29" t="n">
-        <v>4</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>PlPoFin3</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>127</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>13</v>
-      </c>
-      <c r="D30" t="n">
-        <v>4</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>PlPoFin3</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>127</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>14</v>
-      </c>
-      <c r="D31" t="n">
-        <v>4</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
         <is>
           <t>PlPoFin3</t>
         </is>

--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,143 +562,143 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T24_000000_t25OpfVed14.xlsx</t>
+          <t>T24_000000_t27Ved14.xlsx</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>количество организаций получивших убыток за предыдущий год единиц 52</t>
+          <t>в процентах чистая прибыль убыток в ко всем активам 4 6</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>количество организаций единиц</t>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>KolOrgEdi_2</t>
+          <t>PriUby(-DoNalV%K:VsAkt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T24_000000_t25OpfVed14.xlsx</t>
+          <t>T24_000000_t27Ved14.xlsx</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>количество организаций получивших убыток за предыдущий год единиц 52</t>
+          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 4 7</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>количество организаций единиц</t>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>KolOrgEdi_2</t>
+          <t>PriUby(-DoNalV%K:VsAkt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T24_000000_t25OpfVed14.xlsx</t>
+          <t>T24_000000_t27Ved14.xlsx</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>количество организаций получивших убыток за предыдущий год единиц</t>
+          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 0 3</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>количество организаций единиц</t>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>KolOrgEdi_2</t>
+          <t>PriUby(-DoNalV%K:VsAkt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T24_000000_t25OpfVed14.xlsx</t>
+          <t>T24_000000_t27Ved14.xlsx</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>количество организаций получивших убыток за предыдущий год единиц</t>
+          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 3 1</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>количество организаций единиц</t>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>KolOrgEdi_2</t>
+          <t>PriUby(-DoNalV%K:VsAkt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -713,11 +713,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>в процентах чистая прибыль убыток в ко всем активам 4 6</t>
+          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 2 2</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -743,11 +743,11 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 4 7</t>
+          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 15 8</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -766,7 +766,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 0 3</t>
+          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 4 6</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -800,143 +800,143 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T24_000000_t27Ved14.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 3 1</t>
+          <t>поступления по финансовой деятельности всего 377 962 851</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>платежи по инвестиционной деятельности всего</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalV%K:VsAkt</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T24_000000_t27Ved14.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 2 2</t>
+          <t>поступления по финансовой деятельности всего 377 962 851</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>платежи по инвестиционной деятельности всего</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalV%K:VsAkt</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>T24_000000_t27Ved14.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 15 8</t>
+          <t>поступления по финансовой деятельности всего 34 924 952</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.53</v>
+        <v>0.78</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>платежи по финансовой деятельности всего</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalV%K:VsAkt</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>T24_000000_t27Ved14.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 4 6</t>
+          <t>поступления по финансовой деятельности всего 34 924 952</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.53</v>
+        <v>0.78</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>платежи по финансовой деятельности всего</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalV%K:VsAkt</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -944,33 +944,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>поступления по финансовой деятельности всего 377 962 851</t>
+          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности всего</t>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -978,27 +978,27 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>поступления по финансовой деятельности всего 377 962 851</t>
+          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности всего</t>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>PlPoFin3</t>
         </is>
       </c>
     </row>
@@ -1012,27 +1012,27 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
         <v>4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>поступления по финансовой деятельности всего 34 924 952</t>
+          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.78</v>
+        <v>0.61</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности всего</t>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>PlPoFin</t>
+          <t>PlPoFin3</t>
         </is>
       </c>
     </row>
@@ -1046,161 +1046,25 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
         <v>4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>поступления по финансовой деятельности всего 34 924 952</t>
+          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.78</v>
+        <v>0.61</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности всего</t>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
-        <is>
-          <t>PlPoFin</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>127</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>11</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>PlPoFin3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>127</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>12</v>
-      </c>
-      <c r="D21" t="n">
-        <v>4</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>PlPoFin3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>127</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>13</v>
-      </c>
-      <c r="D22" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>PlPoFin3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>127</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>14</v>
-      </c>
-      <c r="D23" t="n">
-        <v>4</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
         <is>
           <t>PlPoFin3</t>
         </is>

--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,509 +562,135 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T24_000000_t27Ved14.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>в процентах чистая прибыль убыток в ко всем активам 4 6</t>
+          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalV%K:VsAkt</t>
+          <t>PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T24_000000_t27Ved14.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 4 7</t>
+          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalV%K:VsAkt</t>
+          <t>PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T24_000000_t27Ved14.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 0 3</t>
+          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalV%K:VsAkt</t>
+          <t>PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T24_000000_t27Ved14.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 3 1</t>
+          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
-        <is>
-          <t>PriUby(-DoNalV%K:VsAkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>96</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>T24_000000_t27Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>9</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 2 2</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>PriUby(-DoNalV%K:VsAkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>96</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>T24_000000_t27Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>9</v>
-      </c>
-      <c r="D10" t="n">
-        <v>14</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 15 8</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>PriUby(-DoNalV%K:VsAkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>97</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>T24_000000_t27Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>9</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 18 чистая прибыль убыток в ко всем активам 4 6</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>PriUby(-DoNalV%K:VsAkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>124</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>38</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>поступления по финансовой деятельности всего 377 962 851</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>платежи по инвестиционной деятельности всего</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>PlPoInvDeyt</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>124</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>38</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>поступления по финансовой деятельности всего 377 962 851</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>платежи по инвестиционной деятельности всего</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>PlPoInvDeyt</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>127</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>поступления по финансовой деятельности всего 34 924 952</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>платежи по финансовой деятельности всего</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>PlPoFin</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>127</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>поступления по финансовой деятельности всего 34 924 952</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>платежи по финансовой деятельности всего</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>PlPoFin</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>127</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>11</v>
-      </c>
-      <c r="D16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>PlPoFin3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>127</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>12</v>
-      </c>
-      <c r="D17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>PlPoFin3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>127</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>13</v>
-      </c>
-      <c r="D18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>PlPoFin3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>127</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>14</v>
-      </c>
-      <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
         <is>
           <t>PlPoFin3</t>
         </is>

--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,35 +460,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14.xlsx</t>
+          <t>T24_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>коммерческие и уравленческие расходы 50 117 067</t>
+          <t>на конец года тысяч рублей себестоимость продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
+          <t>доходы и расходы по обычным видам деятельности за отчетный период себестоимость продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas</t>
+          <t>DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas_1</t>
         </is>
       </c>
     </row>
@@ -502,61 +502,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей себестоимость продаж с учетом коммерческих и управленческих расходов</t>
+          <t>на конец года тысяч рублей прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности за отчетный период себестоимость продаж с учетом коммерческих и управленческих расходов</t>
+          <t>отчетный год чистая прибыль убыток отчетного периода</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas_1</t>
+          <t>OtcGoChiPri(ubOtcPer_1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей прибыль убыток от продаж</t>
+          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>отчетный год чистая прибыль убыток отчетного периода</t>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>OtcGoChiPri(ubOtcPer_1</t>
+          <t>PlPoFin3</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
@@ -657,40 +657,6 @@
         </is>
       </c>
       <c r="H7" t="inlineStr">
-        <is>
-          <t>PlPoFin3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>127</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>14</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
         <is>
           <t>PlPoFin3</t>
         </is>

--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -468,27 +468,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей себестоимость продаж с учетом коммерческих и управленческих расходов</t>
+          <t>коммерческие и управленческие расходы</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности за отчетный период себестоимость продаж с учетом коммерческих и управленческих расходов</t>
+          <t>в том числе управленческие расходы</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas_1</t>
+          <t>DohIRasPoObyVidDeyZaOtcPerVToChiUprRas_1</t>
         </is>
       </c>
     </row>
@@ -502,27 +502,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей прибыль убыток от продаж</t>
+          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>отчетный год чистая прибыль убыток отчетного периода</t>
+          <t>в том числе управленческие расходы</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>OtcGoChiPri(ubOtcPer_1</t>
+          <t>DohIRasPoObyVidDeyZaOtcPerVToChiUprRas_1</t>
         </is>
       </c>
     </row>

--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -539,7 +539,7 @@
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>

--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,69 +460,69 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>коммерческие и управленческие расходы</t>
+          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.73</v>
+        <v>0.57</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>в том числе управленческие расходы</t>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeyZaOtcPerVToChiUprRas_1</t>
+          <t>PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
+          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>в том числе управленческие расходы</t>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeyZaOtcPerVToChiUprRas_1</t>
+          <t>PlPoFin3</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -589,74 +589,6 @@
         </is>
       </c>
       <c r="H5" t="inlineStr">
-        <is>
-          <t>PlPoFin3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>127</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>13</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>PlPoFin3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>127</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>14</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
         <is>
           <t>PlPoFin3</t>
         </is>

--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -468,33 +468,33 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
+          <t>в том числе прочие поступления</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
+          <t>поступления по текущей деятельности прочие поступления</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>PlPoFin3</t>
+          <t>PrTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,33 +502,33 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
+          <t>в том числе прочие поступления</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
+          <t>поступления по текущей деятельности прочие поступления</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PlPoFin3</t>
+          <t>PrTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -536,61 +536,741 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
+          <t>в том числе прочие поступления</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
+          <t>поступления по текущей деятельности прочие поступления</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PlPoFin3</t>
+          <t>PrTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>109</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>в том числе прочие поступления</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>поступления по текущей деятельности прочие поступления</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PrTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>в том числе прочие поступления</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>поступления по текущей деятельности прочие поступления</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PrTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>111</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>в том числе прочие поступления</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>поступления по текущей деятельности прочие поступления</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PrTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>112</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>в том числе прочие поступления</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>поступления по текущей деятельности прочие поступления</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PrTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>в том числе прочие поступления</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>поступления по текущей деятельности прочие поступления</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PrTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>117</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>в том числе прочие поступления</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>поступления по текущей деятельности прочие поступления</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PrTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>117</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>в том числе прочие поступления</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>поступления по текущей деятельности прочие поступления</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PrTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>в том числе прочие поступления</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>поступления по текущей деятельности прочие поступления</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PrTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>119</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>в том числе прочие поступления</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>поступления по текущей деятельности прочие поступления</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PrTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>в том числе прочие поступления</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>поступления по текущей деятельности прочие поступления</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PrTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>в том числе прочие поступления</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>поступления по текущей деятельности прочие поступления</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PrTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>127</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>11</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>12</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>13</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>14</v>
       </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F19" t="n">
         <v>0.57</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>платежи всего</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>платежи по текущей деятельности всего</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>PlatPoTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>платежи всего</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>платежи по текущей деятельности всего</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>PlatPoTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" t="n">
+        <v>18</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>платежи всего</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>платежи по текущей деятельности всего</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>PlatPoTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>18</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>платежи всего</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>платежи по текущей деятельности всего</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>PlatPoTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>9</v>
+      </c>
+      <c r="D24" t="n">
+        <v>33</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>платежи всего</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>платежи по текущей деятельности всего</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>PlatPoTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" t="n">
+        <v>33</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>платежи всего</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>платежи по текущей деятельности всего</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>

--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -528,7 +528,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -562,7 +562,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -876,401 +876,27 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>в том числе прочие поступления</t>
+          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>PrTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>120</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" t="n">
-        <v>13</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>в том числе прочие поступления</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>PrTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>127</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>11</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
           <t>PlPoFin3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>127</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>12</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>PlPoFin3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>127</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>13</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>PlPoFin3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>127</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>14</v>
-      </c>
-      <c r="D19" t="n">
-        <v>3</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>PlPoFin3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>132</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>9</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>платежи всего</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>платежи по текущей деятельности всего</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>PlatPoTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>132</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>10</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>платежи всего</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>платежи по текущей деятельности всего</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>PlatPoTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>132</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>9</v>
-      </c>
-      <c r="D22" t="n">
-        <v>18</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>платежи всего</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>платежи по текущей деятельности всего</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>PlatPoTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>132</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>10</v>
-      </c>
-      <c r="D23" t="n">
-        <v>18</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>платежи всего</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>платежи по текущей деятельности всего</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>PlatPoTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>132</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>9</v>
-      </c>
-      <c r="D24" t="n">
-        <v>33</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>платежи всего</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>платежи по текущей деятельности всего</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>PlatPoTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>132</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>10</v>
-      </c>
-      <c r="D25" t="n">
-        <v>33</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>платежи всего</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>платежи по текущей деятельности всего</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>

--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -468,433 +468,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>в том числе прочие поступления</t>
+          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t>PrTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>108</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>в том числе прочие поступления</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PrTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>109</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>в том числе прочие поступления</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>PrTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>110</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>в том числе прочие поступления</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>PrTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>111</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>в том числе прочие поступления</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>PrTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>112</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>в том числе прочие поступления</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>PrTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>117</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>в том числе прочие поступления</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>PrTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>117</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" t="n">
-        <v>16</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>в том числе прочие поступления</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>PrTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>118</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>6</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>в том числе прочие поступления</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>PrTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>119</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>6</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>в том числе прочие поступления</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>PrTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>120</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>6</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>в том числе прочие поступления</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>PrTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>120</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>6</v>
-      </c>
-      <c r="D13" t="n">
-        <v>13</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>в том числе прочие поступления</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>PrTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>127</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>11</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
         <is>
           <t>PlPoFin3</t>
         </is>

--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -1,34 +1,73 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>table</t>
+  </si>
+  <si>
+    <t>source_file</t>
+  </si>
+  <si>
+    <t>column</t>
+  </si>
+  <si>
+    <t>header_row</t>
+  </si>
+  <si>
+    <t>cell_text</t>
+  </si>
+  <si>
+    <t>score</t>
+  </si>
+  <si>
+    <t>closest_candidate</t>
+  </si>
+  <si>
+    <t>closest_indicator</t>
+  </si>
+  <si>
+    <t>T24_000000_t29Ved14.xlsx</t>
+  </si>
+  <si>
+    <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
+  </si>
+  <si>
+    <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
+  </si>
+  <si>
+    <t>PlPoFin3</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +86,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,91 +380,63 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>table</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>source_file</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>header_row</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>cell_text</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>closest_candidate</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>closest_indicator</t>
-        </is>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:8">
+      <c r="A2">
         <v>127</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
         <v>11</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>3</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2">
         <v>0.57</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>PlPoFin3</t>
-        </is>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -1,73 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>table</t>
-  </si>
-  <si>
-    <t>source_file</t>
-  </si>
-  <si>
-    <t>column</t>
-  </si>
-  <si>
-    <t>header_row</t>
-  </si>
-  <si>
-    <t>cell_text</t>
-  </si>
-  <si>
-    <t>score</t>
-  </si>
-  <si>
-    <t>closest_candidate</t>
-  </si>
-  <si>
-    <t>closest_indicator</t>
-  </si>
-  <si>
-    <t>T24_000000_t29Ved14.xlsx</t>
-  </si>
-  <si>
-    <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-  </si>
-  <si>
-    <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-  </si>
-  <si>
-    <t>PlPoFin3</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -86,13 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -380,63 +408,91 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>source_file</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>header_row</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>cell_text</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>closest_candidate</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>closest_indicator</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2">
-        <v>127</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2">
-        <v>11</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>0.57</v>
       </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PlPoFin3</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,35 +460,1463 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127</v>
+        <v>12</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
+          <t>M25_000000_t10Ved14.xlsx</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>M25_000000_t10Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M25_000000_t10Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>M25_000000_t10Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M25_000000_t10Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M25_000000_t10Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M25_000000_t10Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M25_000000_t10Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M25_000000_t10Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>16</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M25_000000_t10Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>M25_000000_t10Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M25_000000_t10Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M25_000000_t10Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>18</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M25_000000_t10Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>19</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>M25_000000_t10Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>M25_000000_t10Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>20</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>M25_000000_t10Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>20</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>M25_000000_t10Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>21</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>M25_000000_t10Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>21</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>M25_000000_t10Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>оборотные активы</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>OboAkt_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>37</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>M25_000000_t22Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 9 обязательства без заемных средств</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>соотношение собственных и заемных средств</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>SooSobIZaeSre</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>37</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>M25_000000_t22Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 9 обязательства без заемных средств</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>соотношение собственных и заемных средств</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>SooSobIZaeSre</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>38</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>M25_000000_t22Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 9 обязательства без заемных средств</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>соотношение собственных и заемных средств</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>SooSobIZaeSre</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>38</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>M25_000000_t22Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 9 обязательства без заемных средств</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>соотношение собственных и заемных средств</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>SooSobIZaeSre</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>39</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>M25_000000_t22Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 9 обязательства без заемных средств</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>соотношение собственных и заемных средств</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>SooSobIZaeSre</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>39</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>M25_000000_t22Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 9 обязательства без заемных средств</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>соотношение собственных и заемных средств</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>SooSobIZaeSre</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>40</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>M25_000000_t22Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 9 обязательства без заемных средств</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>соотношение собственных и заемных средств</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>SooSobIZaeSre</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>40</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M25_000000_t22Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 9 обязательства без заемных средств</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>соотношение собственных и заемных средств</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SooSobIZaeSre</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>66</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>M25_000000_t23FsVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>75</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>77</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>88</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>M25_000000_t26Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>SebProSUchKomIUprRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>100</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>M25_000000_t26Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>8</v>
+      </c>
+      <c r="D34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>SebProSUchKomIUprRas_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>101</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>M25_000000_t27Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
         <v>11</v>
       </c>
-      <c r="D2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 20 в том числе от выпуска облигаций векселей и других долговых ценных бумаг и др</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>в связи с погашением выкупом векселей и других долговых ценных бумаг возврат кредитов и займов</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>PlPoFin3</t>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>чистая прибыль убыток в ко всем активам</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Pri(ubDoNalV%K:VsAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>102</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>M25_000000_t27Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>9</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Pri(ubDoNalV%K:VsAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>103</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>M25_000000_t27Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>11</v>
+      </c>
+      <c r="D37" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Pri(ubDoNalV%K:VsAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>103</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>M25_000000_t27Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>11</v>
+      </c>
+      <c r="D38" t="n">
+        <v>15</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Pri(ubDoNalV%K:VsAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>104</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>M25_000000_t27Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>14</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Pri(ubDoNalV%K:VsAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>104</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>M25_000000_t27Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>13</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Pri(ubDoNalV%K:VsAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>104</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>M25_000000_t27Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>13</v>
+      </c>
+      <c r="D41" t="n">
+        <v>28</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Pri(ubDoNalV%K:VsAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>105</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>M25_000000_t27Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>8</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Pri(ubDoNalV%K:VsAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>106</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>M25_000000_t27Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>9</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Pri(ubDoNalV%K:VsAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>108</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>M25_000000_t27Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>9</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>чистая прибыль убыток в ко всем активам</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Pri(ubDoNalV%K:VsAkt_1</t>
         </is>
       </c>
     </row>

--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>M25_000000_t23FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C30" t="n">

--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,1061 +460,1061 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.52</v>
+        <v>0.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж 115 544</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.52</v>
+        <v>0.76</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>продолжение таблицы 13 прибыль убыток до налогообложения 448</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.52</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>прибыль убыток до налогооблажения</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>Pri(ubDoNal</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж 319 180</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.52</v>
+        <v>0.76</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>продолжение таблицы 13 прибыль убыток до налогообложения 22 067</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>прибыль убыток до налогооблажения</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>Pri(ubDoNal</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.52</v>
+        <v>0.8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.52</v>
+        <v>0.72</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>прибыль убыток до налогооблажения</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>Pri(ubDoNal</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.52</v>
+        <v>0.8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.52</v>
+        <v>0.72</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>прибыль убыток до налогооблажения</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>Pri(ubDoNal</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.52</v>
+        <v>0.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.52</v>
+        <v>0.72</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>прибыль убыток до налогооблажения</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>Pri(ubDoNal</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж 790 337</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.52</v>
+        <v>0.76</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>продолжение таблицы 13 прибыль убыток до налогообложения 98 565</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>прибыль убыток до налогооблажения</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>Pri(ubDoNal</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.52</v>
+        <v>0.8</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.52</v>
+        <v>0.72</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>прибыль убыток до налогооблажения</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>Pri(ubDoNal</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
         <v>3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.52</v>
+        <v>0.8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
         <v>3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.52</v>
+        <v>0.72</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>прибыль убыток до налогооблажения</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>Pri(ubDoNal</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.52</v>
+        <v>0.8</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.52</v>
+        <v>0.72</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>прибыль убыток до налогооблажения</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>Pri(ubDoNal</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M25_000000_t10Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж 31 417</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.52</v>
+        <v>0.76</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>OboAkt_2</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M25_000000_t22Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>продолжение таблицы 9 обязательства без заемных средств</t>
+          <t>продолжение таблицы 13 прибыль убыток до налогообложения 4 170</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>соотношение собственных и заемных средств</t>
+          <t>прибыль убыток до налогооблажения</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SooSobIZaeSre</t>
+          <t>Pri(ubDoNal</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M25_000000_t22Ved14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>продолжение таблицы 9 обязательства без заемных средств</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>соотношение собственных и заемных средств</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SooSobIZaeSre</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro_1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M25_000000_t22Ved14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>продолжение таблицы 9 обязательства без заемных средств</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>соотношение собственных и заемных средств</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SooSobIZaeSre</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro_1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M25_000000_t22Ved14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
         <v>3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>продолжение таблицы 9 обязательства без заемных средств</t>
+          <t>продолжение таблицы 14 прибыль убыток до налогообложения</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.6</v>
+        <v>0.72</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>соотношение собственных и заемных средств</t>
+          <t>прибыль убыток до налогооблажения</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SooSobIZaeSre</t>
+          <t>Pri(ubDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M25_000000_t22Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>продолжение таблицы 9 обязательства без заемных средств</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>соотношение собственных и заемных средств</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>SooSobIZaeSre</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro_2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M25_000000_t22Ved14.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>продолжение таблицы 9 обязательства без заемных средств</t>
+          <t>уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>соотношение собственных и заемных средств</t>
+          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SooSobIZaeSre</t>
+          <t>SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M25_000000_t22Ved14.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>продолжение таблицы 9 обязательства без заемных средств</t>
+          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>соотношение собственных и заемных средств</t>
+          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SooSobIZaeSre</t>
+          <t>SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M25_000000_t22Ved14.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>продолжение таблицы 9 обязательства без заемных средств</t>
+          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов 3 1</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>соотношение собственных и заемных средств</t>
+          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SooSobIZaeSre</t>
+          <t>SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
         <v>4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
+          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
+          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
+          <t>SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
+          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
+          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeyPriUby(-OtPro_1</t>
+          <t>SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
         <v>4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
+          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
+          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeyPriUby(-OtPro_2</t>
+          <t>SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1525,15 +1525,15 @@
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
+          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0.77</v>
+        <v>0.68</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1548,26 +1548,26 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14mo8.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
         <v>4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
+          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0.77</v>
+        <v>0.68</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1576,115 +1576,115 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SebProSUchKomIUprRas_1</t>
+          <t>SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>M25_000000_t27Ved14.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>чистая прибыль убыток в ко всем активам</t>
+          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Pri(ubDoNalV%K:VsAkt</t>
+          <t>SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>M25_000000_t27Ved14.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
+          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pri(ubDoNalV%K:VsAkt</t>
+          <t>SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>M25_000000_t27Ved14.xlsx</t>
+          <t>M25_000000_t26Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D37" t="n">
         <v>4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
+          <t>уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0.55</v>
+        <v>0.77</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Pri(ubDoNalV%K:VsAkt</t>
+          <t>SebProSUchKomIUprRas_1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1695,15 +1695,15 @@
         <v>11</v>
       </c>
       <c r="D38" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
+          <t>чистая прибыль убыток в ко всем активам</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D39" t="n">
         <v>3</v>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D40" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D41" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D42" t="n">
         <v>3</v>
@@ -1854,7 +1854,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1888,33 +1888,169 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
+        <v>104</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>M25_000000_t27Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>13</v>
+      </c>
+      <c r="D44" t="n">
+        <v>28</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Pri(ubDoNalV%K:VsAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>105</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>M25_000000_t27Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>8</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Pri(ubDoNalV%K:VsAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>106</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>M25_000000_t27Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>9</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Pri(ubDoNalV%K:VsAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>107</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>M25_000000_t27Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Pri(ubDoNalV%K:VsAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
         <v>108</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>M25_000000_t27Ved14mo8.xlsx</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C48" t="n">
         <v>9</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D48" t="n">
         <v>3</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>чистая прибыль убыток в ко всем активам</t>
         </is>
       </c>
-      <c r="F44" t="n">
+      <c r="F48" t="n">
         <v>0.7</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>прибыль убыток до налогообложения в к всем активам</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Pri(ubDoNalV%K:VsAkt_1</t>
         </is>

--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -505,15 +505,15 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж 115 544</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -539,15 +539,15 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>продолжение таблицы 13 прибыль убыток до налогообложения 448</t>
+          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -573,15 +573,15 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж 319 180</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -607,15 +607,15 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>продолжение таблицы 13 прибыль убыток до налогообложения 22 067</t>
+          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -845,15 +845,15 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж 790 337</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -879,15 +879,15 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>продолжение таблицы 13 прибыль убыток до налогообложения 98 565</t>
+          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1389,15 +1389,15 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов 3 1</t>
+          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>11</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>

--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1117,15 +1117,15 @@
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж 31 417</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1151,15 +1151,15 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>продолжение таблицы 13 прибыль убыток до налогообложения 4 170</t>
+          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1305,754 +1305,6 @@
       <c r="H26" t="inlineStr">
         <is>
           <t>DohIRasPoObyVidDeyPriUby(-OtPro_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>88</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>4</v>
-      </c>
-      <c r="D27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>SebProSUchKomIUprRas</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>89</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>4</v>
-      </c>
-      <c r="D28" t="n">
-        <v>4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>SebProSUchKomIUprRas</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>90</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>4</v>
-      </c>
-      <c r="D29" t="n">
-        <v>4</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>SebProSUchKomIUprRas</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>91</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>4</v>
-      </c>
-      <c r="D30" t="n">
-        <v>4</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>SebProSUchKomIUprRas</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>92</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>4</v>
-      </c>
-      <c r="D31" t="n">
-        <v>4</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>SebProSUchKomIUprRas</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>93</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>4</v>
-      </c>
-      <c r="D32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>SebProSUchKomIUprRas</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>93</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>4</v>
-      </c>
-      <c r="D33" t="n">
-        <v>17</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>SebProSUchKomIUprRas</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>94</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>4</v>
-      </c>
-      <c r="D34" t="n">
-        <v>4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>SebProSUchKomIUprRas</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>94</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>4</v>
-      </c>
-      <c r="D35" t="n">
-        <v>17</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>SebProSUchKomIUprRas</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>95</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>4</v>
-      </c>
-      <c r="D36" t="n">
-        <v>4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 19 уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>SebProSUchKomIUprRas</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>100</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>M25_000000_t26Ved14mo8.xlsx</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>8</v>
-      </c>
-      <c r="D37" t="n">
-        <v>4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>себестоимость продаж с учетом коммерческих и управленческих расходов</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>SebProSUchKomIUprRas_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>101</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>M25_000000_t27Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>11</v>
-      </c>
-      <c r="D38" t="n">
-        <v>3</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>чистая прибыль убыток в ко всем активам</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Pri(ubDoNalV%K:VsAkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>102</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>M25_000000_t27Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>9</v>
-      </c>
-      <c r="D39" t="n">
-        <v>3</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Pri(ubDoNalV%K:VsAkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>103</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>M25_000000_t27Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>11</v>
-      </c>
-      <c r="D40" t="n">
-        <v>3</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Pri(ubDoNalV%K:VsAkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>103</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>M25_000000_t27Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>11</v>
-      </c>
-      <c r="D41" t="n">
-        <v>15</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Pri(ubDoNalV%K:VsAkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>104</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>M25_000000_t27Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>14</v>
-      </c>
-      <c r="D42" t="n">
-        <v>3</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Pri(ubDoNalV%K:VsAkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>104</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>M25_000000_t27Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>13</v>
-      </c>
-      <c r="D43" t="n">
-        <v>16</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Pri(ubDoNalV%K:VsAkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>104</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>M25_000000_t27Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>13</v>
-      </c>
-      <c r="D44" t="n">
-        <v>28</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Pri(ubDoNalV%K:VsAkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>105</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>M25_000000_t27Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>8</v>
-      </c>
-      <c r="D45" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Pri(ubDoNalV%K:VsAkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>106</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>M25_000000_t27Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>9</v>
-      </c>
-      <c r="D46" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Pri(ubDoNalV%K:VsAkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>107</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>M25_000000_t27Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>8</v>
-      </c>
-      <c r="D47" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Pri(ubDoNalV%K:VsAkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>108</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>M25_000000_t27Ved14mo8.xlsx</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>9</v>
-      </c>
-      <c r="D48" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>чистая прибыль убыток в ко всем активам</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Pri(ubDoNalV%K:VsAkt_1</t>
         </is>
       </c>
     </row>

--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,7 +528,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -536,33 +536,33 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогооблажения</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pri(ubDoNal</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -596,7 +596,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -604,33 +604,33 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогооблажения</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pri(ubDoNal</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -672,33 +672,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогооблажения</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pri(ubDoNal</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -740,33 +740,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогооблажения</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pri(ubDoNal</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -808,44 +808,44 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогооблажения</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pri(ubDoNal</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -862,58 +862,58 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro_1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
+          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогооблажения</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pri(ubDoNal</t>
+          <t>DohIRasPoObyVidDeyPriUby(-OtPro_1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -929,380 +929,6 @@
         </is>
       </c>
       <c r="H15" t="inlineStr">
-        <is>
-          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>72</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогооблажения</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Pri(ubDoNal</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>73</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>73</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>5</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогооблажения</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Pri(ubDoNal</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>73</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>11</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>73</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>5</v>
-      </c>
-      <c r="D20" t="n">
-        <v>11</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогооблажения</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Pri(ubDoNal</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>74</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>DohIRasPoObyVidDeyPriUby(-OtPro</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>74</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>5</v>
-      </c>
-      <c r="D22" t="n">
-        <v>3</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 13 прибыль убыток до налогообложения</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогооблажения</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Pri(ubDoNal</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>75</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" t="n">
-        <v>5</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>DohIRasPoObyVidDeyPriUby(-OtPro_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>76</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>2</v>
-      </c>
-      <c r="D24" t="n">
-        <v>3</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>DohIRasPoObyVidDeyPriUby(-OtPro_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>76</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 14 прибыль убыток до налогообложения</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогооблажения</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Pri(ubDoNal_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>77</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14mo8.xlsx</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" t="n">
-        <v>4</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>доходы и расходы по обычным видам деятельности затраты на производство продаж</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
         <is>
           <t>DohIRasPoObyVidDeyPriUby(-OtPro_2</t>
         </is>

--- a/output/нужна_проверка.xlsx
+++ b/output/нужна_проверка.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,380 +455,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>closest_indicator</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>93</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>предыдущий год сопоставимый круг прибыль убыток от продолжающейся деятельности до налогообложения</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>94</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>предыдущий год сопоставимый круг прибыль убыток от продолжающейся деятельности до налогообложения</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>95</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>предыдущий год сопоставимый круг прибыль убыток от продолжающейся деятельности до налогообложения</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>95</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>предыдущий год сопоставимый круг прибыль убыток от продолжающейся деятельности до налогообложения</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>96</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>предыдущий год сопоставимый круг прибыль убыток от продолжающейся деятельности до налогообложения</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>97</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>предыдущий год сопоставимый круг прибыль убыток от продолжающейся деятельности до налогообложения</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>98</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>предыдущий год сопоставимый круг прибыль убыток от продолжающейся деятельности до налогообложения</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>99</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>предыдущий год сопоставимый круг прибыль убыток от продолжающейся деятельности до налогообложения</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>100</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>предыдущий год сопоставимый круг прибыль убыток от продолжающейся деятельности до налогообложения</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>101</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>предыдущий год сопоставимый круг прибыль убыток от продолжающейся деятельности до налогообложения</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>102</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>прибыль убыток до налогообложения</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>предыдущий год сопоставимый круг прибыль убыток от продолжающейся деятельности до налогообложения</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
         </is>
       </c>
     </row>
